--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-018_月次集計取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-018_月次集計取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="12039600"/>
+    <ext cx="8572500" cy="12239625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-018 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-018 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -954,7 +954,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
+    <row r="10" ht="49" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>INFO</t>
@@ -977,7 +977,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>AdminReportController#monthly（by = JWT の sub。取得に @AuthenticationPrincipal Jwt jwt を引数に追加）</t>
+          <t>AdminReportController#monthly（by = JWT の sub。取得に Authentication auth を引数に追加）</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="124" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2085,7 +2085,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：共通基盤の定義元を ONL-001 に統一、handleBadParam を handleTypeMismatch に名称統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：共通基盤の定義元を ONL-001 に統一、handleBadParam を handleTypeMismatch に名称統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・Controller は Authentication#getName()、権限は @PreAuthorize("hasRole('ADMIN')")</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3968,7 +3970,7 @@
     @RequestParam(required = false) String month,
     @RequestParam(required = false) Long departmentId,
     @RequestParam(required = false, defaultValue = "json") String format,
-    @AuthenticationPrincipal Jwt jwt)</t>
+    Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4092,17 +4094,17 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>@AuthenticationPrincipal。CSV 出力ログの操作者 ID（sub）用</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -4157,7 +4159,7 @@
 if (!csv) return ResponseEntity.ok(res);                  // ⑦ No
 byte[] body = reportService.toCsv(res);                   // ⑧
 log.info("Monthly report exported month={} departmentId={} rows={} by={}",
-    ym, departmentId, res.rows().size(), Long.valueOf(jwt.getSubject()));
+    ym, departmentId, res.rows().size(), Long.valueOf(auth.getName()));
 return ResponseEntity.ok()                                // ⑨
     .contentType(new MediaType("text", "csv", StandardCharsets.UTF_8))
     .header(HttpHeaders.CONTENT_DISPOSITION, ContentDisposition.attachment()
